--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
           <t>สำนักงานพิพิธภัณฑ์เกษตรเฉลิมพระเกียรติพระบาทสมเด็จพระเจ้าอยู่หัว (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0719</t>
-        </is>
+      <c r="C2" t="n">
+        <v>719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +511,8 @@
           <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0915</t>
-        </is>
+      <c r="C3" t="n">
+        <v>915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -550,10 +546,8 @@
           <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -587,29 +581,360 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5c1c7a5-d202-4260-a28c-7873e25c3d14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจัดจ้างบำรุงรักษาระบบป้องกันภัยคุมคามทางไซเบอร์ของระบบเครือข่ายและคอมพิวเตอร์ จำนวน 1 งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f929dc8d-821f-4044-8a38-f29e059da057</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d42ed1e9-d596-4629-9a7e-4126f296b5cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์สำหรับการเข้ารับการอบรมและทดสอบใบอนุญาตขับรถ (Q) ศูนย์ควบคุมระบบตรวจสภาพ (VICC) ศูนย์ GPS ระบบ DLT Traffic Ticket ระบบ Smart Bus Terminal และเครื่องคอมพิวเตอร์ที่ใช้สนับสนุนผู้ปฏิบัติงานเพื่อออกใบอนุญาตขับรถทั้งส่วนกลางและส่วนภูมิภาค ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=20929fbd-ffa4-4e24-b4c6-3507890000a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง ประเภทเรือหางยาวสำหรับการลาดตระเวนพื้นที่ทางน้ำ เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานอุทยานแห่งชาติเขาแหลม จังหวัดกาญจนบุรี  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ddad95eb-5363-49ae-82c5-85f620397840</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างโครงการก่อสร้างรั้วคอนกรีตเสริมเหล็กพร้อมป้ายชื่อที่ว่าการอำเภอโนนนารายณ์ ตำบลหนองหลวง อำเภอโนนนารายณ์ จังหวัดสุรินทร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>★ (ป้ายชื่อ)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad452e64-7fe2-4385-899d-81d2ef011673</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>กรมราชทัณฑ์</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อระบบกล้องวงจรปิด พร้อมติดตั้ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>★ (กล้องวงจรปิด)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d2c7ad2f-57f5-4aac-b2a9-f72982214517</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>สถาบันเทคโนโลยีนิวเคลียร์แห่งชาติ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเครื่องคอมพิวเตอร์พกพาและอุปกรณ์ต่อพ่วง ระยะเวลา ๓ ปี จำนวน ๑ โครงการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, คอมพิวเตอร์พกพา)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=53a14f17-fb66-4dbd-b546-ce9b155968c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รักษา รายการเครื่องติดตามสัญญาณชีพอัตโนมัติและตรวจคลื่นไฟฟ้าหัวใจแบบวิเคราะห์ผล 12 ลีด เพื่อเชื่อมต่อระบบการแพทย์ทางไกลสำหรับผู้ป่วยวิกฤติในแผนฉุกเฉินและเชื่อมต่อระบบข้อมูลโรงพยาบาล จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a5c1c7a5-d202-4260-a28c-7873e25c3d14</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7e2dc072-1972-41e6-91b5-062b1991682e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการกล้องส่องตรวจท่อทางเดินน้ำดีและตับอ่อนชนิดวิดิทัศน์แบบคมชัดสูงพร้อมชุดควบคุมสัญญาณภาพ จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0532beec-8892-499a-81e9-bddcf694ed59</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,10 +616,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C6" t="n">
+        <v>705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -653,10 +651,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C7" t="n">
+        <v>712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -690,10 +686,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C8" t="n">
+        <v>804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -727,10 +721,8 @@
           <t>กรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0909</t>
-        </is>
+      <c r="C9" t="n">
+        <v>909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -764,10 +756,8 @@
           <t>กรมการปกครอง</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -801,10 +791,8 @@
           <t>กรมราชทัณฑ์</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1607</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -838,10 +826,8 @@
           <t>สถาบันเทคโนโลยีนิวเคลียร์แห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -875,10 +861,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -912,29 +896,804 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการกล้องส่องตรวจท่อทางเดินน้ำดีและตับอ่อนชนิดวิดิทัศน์แบบคมชัดสูงพร้อมชุดควบคุมสัญญาณภาพ จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0532beec-8892-499a-81e9-bddcf694ed59</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน ๒ ล้อ แบบดับเบิ้ลแค็บ จำนวน ๒ คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=147f5656-122f-4201-8cec-eaddea6d2c0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างจัดทำพร้อมติดตั้ง เครื่องสูบน้ำ , มอเตอร์ไฟฟ้า , ปั๊ม , ตู้ควบคุมไฟฟ้า และอุปกรณ์ประกอบต่างๆ Spec.No.S 5 321 0302 0461 1 สำนักเครื่องจักรกล สำหรับงาน สถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำ บ้านศรีสุข (แห่งที่ 2) ตำบลขามเปี้ย อำเภอตระการพืชผล จังหวัดอุบลราชธานี (คป.อุบลราชธานี) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bbbf3b10-9af3-481f-9a1b-d6cf53d88635</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง  รถบรรทุก (ดีเซล) ขนาด 2 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,700 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 75 กิโลวัตต์ แบบ 4 ล้อ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fac2980-5f9a-43b7-a581-bcc3980059df</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาที่ดิน</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0708</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาระบบคอมพิวเตอร์และอุปกรณ์ กรมพัฒนาที่ดิน ประจำปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a9ba60c4-4885-49e0-9ab3-a1a87c455034</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถบรรทุก (ดีเซล) ขนาด 1 ตันปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม จำนวน 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3b2d2e74-99fe-4255-b158-34632c8102f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ยานพาหนะและขนส่ง รายการรถบรรทุก (ดีเซล) ขนาด ๑ ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า ๒,๔๐๐ ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า ๑๑๐ กิโลวัตต์ ขับเคลื่อน ๒ ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคารถบรรทุก ขนาด ๑ ตัน หลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานสหกรณ์จังหวัดสุโขทัย ตำบลธานี อำเภอเมืองสุโขทัย จังหวัดสุโขทัย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ecc02d1-95bc-41e6-afac-55fdf2be9eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์รถโดยสารขนาด 12 ที่นั่ง (ดีเซล) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=098e1a34-64d8-49e2-a0d6-1cd8fdaf7c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างดูแลและบำรุงรักษาระบบเครือข่ายคอมพิวเตอร์ของกรมส่งเสริมสหกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7d809559-53a8-4838-905e-6bda70dca8ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์และระบบงานใบอนุญาตประกอบการขนส่งอิเล็กทรอนิกส์ (DLT E-Transport License  ETL) ประจำปีงบประมาณ พ.ศ. 2570 ครั้งที่ 2  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f2226447-34e8-45be-9776-6b030fee414e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาระบบการควบคุม กำกับ ดูแลโรงเรียนสอนขับรถด้วยระบบอิเล็กทรอนิกส์ (e-Classroom) สำหรับการบำรุงรักษาระบบคอมพิวเตอร์และอุปกรณ์ ประจำปีงบประมาณ พ.ศ. 2570  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2b9af18a-ff99-457a-8851-6922e8e483d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำรวจ และเครื่องคอมพิวเตอร์ พร้อมโปรแกรมประมวลผลเชิงวิทยาศาสตร์ สำหรับประมวลผลข้อมูล GNSS รวม ๓ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=020804a8-34cf-43b8-8957-41a61df3de35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๑๑ รายการ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ca3ee44-1ac0-4f94-b857-81c0f0f6c88b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการกล้องส่องตรวจท่อทางเดินน้ำดีและตับอ่อนชนิดวิดิทัศน์แบบคมชัดสูงพร้อมชุดควบคุมสัญญาณภาพ จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0532beec-8892-499a-81e9-bddcf694ed59</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์สนับสนุน รายการเตียงผู้ป่วยสำหรับไอซียูปรับด้วยไฟฟ้าชนิด 4 motor จำนวน 4 เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=80051615-d5b8-43cb-b3ef-1304b3b99eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รักษา รายการกล้องจุลทรรศน์ สำหรับผ่าตัดตาพร้อมระบบบันทึกวีดิทัศน์ จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=17519804-6d2c-4ea0-adc5-f712a3af454e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์การแพทย์ รายการ เตียงผ่าตัดทั่วไประบบไฟฟ้า พร้อมรีโมทคอนโทรล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=aa52176e-ff97-498e-b131-4346af40ecc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิดสี ๒ หัวตรวจ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b76d91c7-92e1-4172-9612-61f6c1cdb41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูง ระดับความคมชัดสูง ๓ หัวตรวจ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6fa0b14f-621f-49f3-b127-29edea193524</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ กล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=24270e33-78e0-4092-9776-78c8df643c47</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการชุดตรวจสุขภาพระบบแพทย์ทางไกลแบบพกพา พร้อมระบบบริหารจัดการข้อมูลส่วนกลางและแอพพลิเคชั่นข้อมูลสุขภาพส่วนบุคคล ของโรงพยาบาลชุมชน 4 แห่ง, โรงพยาบาลส่งเสริมสุขภาพตำบล 39 แห่ง และสถานีอนามัยเฉลิมพระเกียรติฯบ้านรุน จำนวน 66 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db8d5d33-2a2d-40ca-9e77-3302f2b8750a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ กล้องส่องตรวจลำไส้ใหญ่ชนิดวีดิทัศน์แบบคมชัดสูงพร้อมชุดควบคุมสัญญาณภาพ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa6fb688-518a-4b06-b14e-063fdb5a50ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การแพทย์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d076096c-a85d-4329-8870-72a1df4458f6</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,10 +931,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C15" t="n">
+        <v>307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -968,10 +966,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C16" t="n">
+        <v>703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1005,10 +1001,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C17" t="n">
+        <v>705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1042,10 +1036,8 @@
           <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0708</t>
-        </is>
+      <c r="C18" t="n">
+        <v>708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1079,10 +1071,8 @@
           <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+      <c r="C19" t="n">
+        <v>711</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1116,10 +1106,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C20" t="n">
+        <v>712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1153,10 +1141,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C21" t="n">
+        <v>712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1190,10 +1176,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C22" t="n">
+        <v>712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1227,10 +1211,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C23" t="n">
+        <v>804</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1264,10 +1246,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C24" t="n">
+        <v>804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1301,10 +1281,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1338,10 +1316,8 @@
           <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1375,10 +1351,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2102</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1412,10 +1386,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1449,10 +1421,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2102</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1486,10 +1456,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C30" t="n">
+        <v>2102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1523,10 +1491,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C31" t="n">
+        <v>2102</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1560,10 +1526,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2102</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1597,10 +1561,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C33" t="n">
+        <v>2102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1596,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1671,29 +1631,434 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การแพทย์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d076096c-a85d-4329-8870-72a1df4458f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่งรถโดยสารขนาด 12 ที่นั่ง (ดีเซล) จำนวน 1 คัน และรถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 4 ล้อ แบบดับเบิ้ลแค็บพร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาส จำนวน 1 คัน ของสำนักงานสหกรณ์จังหวัดเชียงใหม่  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4bf6db4f-e884-4772-9d7a-a356e58f72ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าเช่าเครื่องคอมพิวเตอร์เพื่อทดแทนเครื่องเช่าที่หมดสัญญาและรองรับการขยายตัวของงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d79a9bf0-54b3-48aa-815e-41eed39b2214</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การแพทย์ จำนวน 8 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d076096c-a85d-4329-8870-72a1df4458f6</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องวัดความดันโลหิตชนิดอัตโนมัติ พร้อมวัดความอิ่มตัวของออกซิเจนในเลือด ของโรงพยาบาลชุมชน 5 แห่ง และโรงพยาบาลส่งเสริมสุขภาพตำบล 21 แห่ง จำนวน 49 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f71ab11d-ea76-441e-83ee-37685b2d6869</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์การแพทย์เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ จำนวน 2 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3fcbb487-519d-4070-adbd-350acd0dc0a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการกล้องถ่ายภาพจอประสาทตาดิจิตอล จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=577221f6-01bf-46c7-b537-4419efb1a371</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 8 เตียง จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1f4d74f0-f07d-46bc-988b-7627b14889c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 3 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b72172-85bc-4892-844d-beceb96e4999</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=80c30fd9-b433-425b-b00b-85411e319ce4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องแม่ข่ายและระบบสำรองข้อมูลขนาดใหญ่สำหรับ DR-Site ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (เครื่องแม่ข่าย)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ea2b5592-e903-46e2-890e-351b39083f40</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>กรมควบคุมโรค</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ไฟฟ้าและวิทยุ ระบบผลิตไฟฟ้าจากพลังงานแสงอาทิตย์บนหลังคา (Solar Rooftop) 120 กิโลวัตต์ และติดตั้ง CT VT (Solar Rooftop) จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=85eef24e-3904-4482-92ef-d75f4169c7b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ทางการแพทย์ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงระดับความคมชัด ๓ หัวตรวจ ของโรงพยาบาลส่งเสริมสุขภาพ ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ พ.ศ. ๒๕๗๐ จำนวน ๑ รายการ ( จำนวน ๑ เครื่อง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8d458296-9e1c-4dc7-a96a-d79f4270c2d6</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C36" t="n">
+        <v>712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1703,10 +1701,8 @@
           <t>สำนักงานนวัตกรรมแห่งชาติ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
+      <c r="C37" t="n">
+        <v>1913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1740,10 +1736,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1777,10 +1771,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C39" t="n">
+        <v>2102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1814,10 +1806,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C40" t="n">
+        <v>2102</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1851,10 +1841,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C41" t="n">
+        <v>2102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1888,10 +1876,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1925,10 +1911,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1962,10 +1946,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C44" t="n">
+        <v>2102</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1999,10 +1981,8 @@
           <t>กรมควบคุมโรค</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
+      <c r="C45" t="n">
+        <v>2104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2036,10 +2016,8 @@
           <t>กรมอนามัย</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
+      <c r="C46" t="n">
+        <v>2109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2059,6 +2037,413 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=8d458296-9e1c-4dc7-a96a-d79f4270c2d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตามโครงการจัดหาครุภัณฑ์คอมพิวเตอร์ และอุปกรณ์ ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=66da9630-4728-4931-9950-76108e8667c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาที่ดิน</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0708</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกล ปีงบประมาณ ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=800017d5-9368-4e62-864c-256fa7c74d6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0712</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาบรรทุกขนาด 1 ตัน หลังคาไฟเบอร์กลาสหรือเหล็กหรือพลาสติกวิศวกรรม ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=221e88ed-a8fd-4c8d-9d87-4ce01e91cdae</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์โน้ตบุ๊ก สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับเครื่องคอมพิวเตอร์โน้ตบุ๊ก แบบสิทธิการใช้งานประเภทติดตั้งมาจากโรงงาน (OEM) และชุดโปรแกรมจัดการสำนักงานแบบที่ 1 ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย แขวงรองเมือง เขตปทุมวัน กรุงเทพมหานคร 35 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ระบบปฏิบัติการ)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d46fdd27-0eec-44fc-a430-86bf96c44312</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>กรมการค้าภายใน</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่าย (Server) เครื่องคอมพิวเตอร์ และ LAN Cable ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ea7dd63b-0240-46fc-a592-da15747e08eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์โคมไฟผ่าตัดใหญ่โคมคู่ ความสว่างไม่น้อยกว่า 130,000 ลักซ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=944f2737-257d-4e49-ad79-c864f5d3313c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดใหญ่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=828e96c3-d216-44b4-96bc-d0968510cb5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงชนิด 2 หัวตรวจ จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f93f2f1f-e4f2-40a1-b460-6f635e18edda</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์การแพทย์รายการเครื่องช่วยนวดหัวใจและฟื้นคืนชีพผู้ป่วยอัตโนมัติ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3abb381e-7167-4bb4-a726-47188ee34715</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อซื้อครุภัณฑ์การแพทย์รายการเครื่องตรวจอวัยวะภายในด้วยคลื่นเสียงความถี่สูงระดับความคมชัดสูง 3 หัวตรวจ ชนิดเคลื่อนย้ายได้ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0a5d2873-22cb-4ef9-943c-bc3f9d88a9f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ โคมไฟผ่าตัดใหญ่โคมคู่ ความสว่างไม่น้อยกว่า 130,000 ลักซ์ หลอดแอลอีดี จำนวน 1 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5b2aa31c-80fc-45dd-a52c-97efa2512958</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,10 +2051,8 @@
           <t>กรมตรวจบัญชีสหกรณ์</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0704</t>
-        </is>
+      <c r="C47" t="n">
+        <v>704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2088,10 +2086,8 @@
           <t>กรมพัฒนาที่ดิน</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0708</t>
-        </is>
+      <c r="C48" t="n">
+        <v>708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2125,10 +2121,8 @@
           <t>กรมส่งเสริมสหกรณ์</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0712</t>
-        </is>
+      <c r="C49" t="n">
+        <v>712</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2162,10 +2156,8 @@
           <t>กรมพัฒนาพลังงานทดแทนและอนุรักษ์พลังงาน</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="C50" t="n">
+        <v>1205</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2199,10 +2191,8 @@
           <t>กรมการค้าภายใน</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
+      <c r="C51" t="n">
+        <v>1304</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2236,10 +2226,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C52" t="n">
+        <v>2102</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2273,10 +2261,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2102</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2310,10 +2296,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C54" t="n">
+        <v>2102</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2347,10 +2331,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C55" t="n">
+        <v>2102</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2384,10 +2366,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C56" t="n">
+        <v>2102</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2421,29 +2401,508 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ โคมไฟผ่าตัดใหญ่โคมคู่ ความสว่างไม่น้อยกว่า 130,000 ลักซ์ หลอดแอลอีดี จำนวน 1 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5b2aa31c-80fc-45dd-a52c-97efa2512958</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0206</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโต๊ะนักเรียนพร้อมเก้าอี้ จำนวน ๘๓๐ ชุด (แจ้งที่ ๒/๗๐) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0f27f3c3-42f0-4c77-8528-4955e2eadde3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องพิมพ์แผนที่ดิจิทัล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>★ (เครื่องพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=51a59485-8a5d-4f8c-acf6-3cf344f1027a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>กรมสรรพากร</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจัดจ้างบริการดูแลบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์คอมพิวเตอร์ พร้อมอุปกรณ์ต่อพ่วงต่าง ๆ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0085e7f3-c2b1-44b6-8297-da42d02ef357</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว รายการเครื่องซักผ้า แบบอุตสาหกรรม ขนาด ๕๐ ปอนด์ จำนวน ๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b1e3f65a-964b-41f1-9004-9f0834d7e7ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=83b34ddd-a162-4d30-ad0b-90fa8d1a9447</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ จำนวน ๒ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3f282b80-dedb-4cff-ac7b-dcc82a1006d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์ยานพาหนะและขนส่ง รถบรรทุก (ดีเซล) ขนาด 1 ตัน ปริมาตรกระบอกสูบไม่ต่ำกว่า 2,400 ซีซี หรือกำลังเครื่องยนต์สูงสุดไม่ต่ำกว่า 110 กิโลวัตต์ ขับเคลื่อน 2 ล้อ แบบดับเบิ้ลแค็บ พร้อมหลังคาไฟเบอร์กลาส  หรือเหล็กหรือพลาสติกวิศวกรรม สำนักงานเกษตรอำเภอเมืองปทุมธานี ตำบลบ้านฉาง อำเภอเมืองปทุมธานี   จังหวัดปทุมธานี 1 คัน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5f9697fe-a260-45d9-9071-adfab3b2a579</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ โคมไฟผ่าตัดใหญ่โคมคู่ ความสว่างไม่น้อยกว่า 130,000 ลักซ์ หลอดแอลอีดี จำนวน 1 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>★ (ครุภัณฑ์)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5b2aa31c-80fc-45dd-a52c-97efa2512958</t>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ ๖ พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า ๔ เตียง  จำนวน  ๖  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ade3ae32-d9c1-4cb3-bcc1-87f9cce690a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ทันตกรรม จำนวน ๑ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลเจ้าคุณไพบูลย์ พนมทวน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=563805f3-6fb6-4453-be45-8fe63039c21d</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพอัตโนมัติ ขนาดกลาง  จำนวน ๔๒ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=86bf7540-b360-41ba-9423-c45f6aab4856</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์วินิจฉัย รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 4 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=9148e539-fe7a-4788-a5bc-31d38a981a4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องตรวจวิเคราะห์ค่าชีวเคมีในเลือดอัตโนมัติชนิดพกพา ของโรงพยาบาลชุมชน 5 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ed870fbe-4187-42b5-be52-793e8d65bbb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์วิทยาศาสตร์ รายการชุดบำบัดน้ำเสียพร้อมติดตั้ง ศูนย์อนามัยที่ ๖ ชลบุรี ปีงบประมาณ ๒๕๗๐ จำนวน ๑ รายการ โดยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-Bidding) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbaaebde-d156-47ae-9ad2-adf000faa8d6</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202610.xlsx
+++ b/Backup/eGP_Monthly_Main_202610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2436,10 +2436,8 @@
           <t>กองทัพอากาศ</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>0206</t>
-        </is>
+      <c r="C58" t="n">
+        <v>206</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2473,10 +2471,8 @@
           <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+      <c r="C59" t="n">
+        <v>208</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2510,10 +2506,8 @@
           <t>กรมสรรพากร</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0307</t>
-        </is>
+      <c r="C60" t="n">
+        <v>307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2547,10 +2541,8 @@
           <t>กรมพัฒนาสังคมและสวัสดิการ</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
+      <c r="C61" t="n">
+        <v>603</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2584,10 +2576,8 @@
           <t>กรมปศุสัตว์</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+      <c r="C62" t="n">
+        <v>706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2621,10 +2611,8 @@
           <t>กรมปศุสัตว์</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+      <c r="C63" t="n">
+        <v>706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2658,10 +2646,8 @@
           <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+      <c r="C64" t="n">
+        <v>711</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2695,10 +2681,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C65" t="n">
+        <v>2102</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2732,10 +2716,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C66" t="n">
+        <v>2102</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2769,10 +2751,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C67" t="n">
+        <v>2102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2806,10 +2786,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C68" t="n">
+        <v>2102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2843,10 +2821,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C69" t="n">
+        <v>2102</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2880,10 +2856,8 @@
           <t>กรมอนามัย</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
+      <c r="C70" t="n">
+        <v>2109</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2903,6 +2877,820 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fbaaebde-d156-47ae-9ad2-adf000faa8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์สำหรับโครงการพัฒนาระบบสารสนเทศเพื่อการวิเคราะห์ข้อมูลด้านเศรษฐกิจการเงิน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=95dad06a-805d-4cde-be65-cc47408b55f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0502</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์และวัสดุ จำนวน 4 รายการ ของกองมาตรฐานและกำกับความปลอดภัยด้านการท่องเที่ยว สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b01ba179-62d7-4a73-8c9d-ded5cc295733</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=197a1c3c-5283-4b24-8e6e-9518a6dc05cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๒ รายการ เป็นเงิน ๖๔๕,๐๐๐.๐๐ บาท ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0b995920-2d30-4999-92a8-373d486d7ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อเครื่องคอมพิวเตอร์โน๊ตบุ๊ค สำหรับงานประมวลผล พร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับคอมพิวเตอร์และเครี่องคอมพิวเตอร์โน๊ตบุ๊ค แบบสิทธิการใช้งานภายในสำนักงาน ประเภทติดตั้งมาจากโรงงาน (OEM) ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย ชุดโปรแกรมจัดการสำนักงาน แบบที่ 2   ที่มีลิขสิทธิ์ถูกต้องตามกฎหมาย และชุดโปรแกรมป้องกันไวรัส จำนวน 21 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน๊ตบุ๊ค, ระบบปฏิบัติการ, โปรแกรมป้องกันไวรัส)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=34c7697c-a43d-43a6-a0e3-8a5fddcca1fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>กรมตรวจบัญชีสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0704</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ พร้อมชุดโปรแกรมปฎิบัติงาน โปรแกรมจัดการสำนักงาน และโปรแกรมป้องกันไวรัส จำนวน 18 ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61c95af4-cfb5-4cf9-9b51-7ee7e2cd74b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน 3 รายการ  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0311925b-1062-4cbd-a264-bb528f9d0fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>กรมฝนหลวงและการบินเกษตร</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0721</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างค่าบำรุงรักษาระบบคอมพิวเตอร์หรือระบบสารสนเทศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e5386f52-c0cd-4eec-b72a-73ff0cb9687c</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์พร้อมอุปกรณ์ของระบบการออกใบอนุญาตขับรถแบบอิเล็กทรอนิกส์ทั้งส่วนกลางและส่วนภูมิภาค และระบบบริหารจัดการด้านความปลอดภัยทางถนน ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=67c21057-7b9b-448b-8afb-f59d957f930e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์อุปกรณ์เครือข่าย และซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย, ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4d770da4-8bb8-4dfe-809e-a9d86efe8531</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>กรมการเปลี่ยนแปลงสภาพภูมิอากาศและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0908</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างผลิตและเผยแพร่สื่อโทรทัศน์และสื่อออนไลน์ยอดนิยม สร้างการรับรู้ด้านทรัพยากรธรรมชาติสิ่งแวดล้อม และการปรับตัวต่อสภาพภูมิอากาศ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=704bf6f4-d968-47ab-8e79-11ce5020d33f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าระบบจัดการข้อมูลจราจรคอมพิวเตอร์ (Log Management) ผูกพัน 3 ปี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=90171a07-d928-4904-a4cf-f08e5686a00e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อลิขสิทธิ์คอมพิวเตอร์สำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60052ccc-a815-48ec-a948-47adbc75da5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>กรมการปกครอง</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างก่อสร้างรั้วคอนกรีตเสริมเหล็กพร้อมป้ายชื่อที่ว่าการอำเภอโนนนารายณ์ ตำบลหนองหลวง อำเภอโนนนารายณ์ จังหวัดสุรินทร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>★ (ป้ายชื่อ)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad051b78-48d5-47bb-81ed-56d3d9547bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 7 รายการ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d8a3a30c-badd-4f31-ac0b-5e9c2dab61cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการปกครองท้องถิ่น</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ สำนักงานท้องถิ่นจังหวัดลำพูน จำนวน 7 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4afd7759-31d0-4ef2-84e2-07950f0552a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08f77454-585a-4732-be2b-458dbf3eb87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>สถาบันมาตรวิทยาแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อระบบคอมพิวเตอร์แม่ข่ายพร้อมชุดโปรแกรมระบบปฏิบัติการสำหรับเครื่องคอมพิวเตอร์แม่ข่าย (Server) รองรับระบบดิจิทัล ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bbea2329-9993-48ac-909c-a40e7ba613cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการ เครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ ๔ พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า ๔ เตียง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fa65507a-9df1-4b37-987b-8ac8fee093ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>สำนักงานเศรษฐกิจอุตสาหกรรม</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2208</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์เครือข่ายและอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1b00b605-b8c9-4d33-a63b-0c70c64ce78d</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>สำนักงานส่งเสริมวิสาหกิจขนาดกลางและขนาดย่อม</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบและเครื่องคอมพิวเตอร์อุปกรณ์ต่อพ่วงสำนักงาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4c9c226d-2f54-4029-b522-50110576cd98</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>สำนักงานส่งเสริมวิสาหกิจขนาดกลางและขนาดย่อม</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจอคอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e8aaf438-f48e-4a85-abd5-b6d800d065d4</t>
         </is>
       </c>
     </row>
